--- a/src/teams.xlsx
+++ b/src/teams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a2db4df0a309fda/Labs/ConcourCast/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{C52A6B2E-3AE3-3848-B1F7-02D66D633EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0101D6A8-B57C-404B-910C-89146987AC25}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{C52A6B2E-3AE3-3848-B1F7-02D66D633EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C786DE34-DED1-0544-9C13-A7ACAD0148EC}"/>
   <bookViews>
     <workbookView xWindow="16180" yWindow="660" windowWidth="14060" windowHeight="17480" xr2:uid="{76B42AAD-E78D-5C47-A529-CA0D1ECA81C5}"/>
   </bookViews>
@@ -213,6 +213,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>469900</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F595710C-0CF8-AC43-5958-7CA25CE5CFE9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3327400" y="241300"/>
+          <a:ext cx="2044700" cy="6311900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -791,6 +840,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/src/teams.xlsx
+++ b/src/teams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a2db4df0a309fda/Labs/ConcourCast/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{C52A6B2E-3AE3-3848-B1F7-02D66D633EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C786DE34-DED1-0544-9C13-A7ACAD0148EC}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{C52A6B2E-3AE3-3848-B1F7-02D66D633EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F83A869F-DA96-BF4C-80F9-BFE5DC59B8C1}"/>
   <bookViews>
     <workbookView xWindow="16180" yWindow="660" windowWidth="14060" windowHeight="17480" xr2:uid="{76B42AAD-E78D-5C47-A529-CA0D1ECA81C5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="42">
   <si>
     <t>TeamName</t>
   </si>
@@ -160,6 +160,9 @@
   </si>
   <si>
     <t>Glasgow</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
 </sst>
 </file>
@@ -213,55 +216,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>469900</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F595710C-0CF8-AC43-5958-7CA25CE5CFE9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3327400" y="241300"/>
-          <a:ext cx="2044700" cy="6311900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -792,7 +746,7 @@
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -800,7 +754,7 @@
         <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
@@ -808,7 +762,7 @@
         <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -816,7 +770,7 @@
         <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -824,7 +778,7 @@
         <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -832,7 +786,7 @@
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
@@ -840,7 +794,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/src/teams.xlsx
+++ b/src/teams.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a2db4df0a309fda/Labs/ConcourCast/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{C52A6B2E-3AE3-3848-B1F7-02D66D633EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F83A869F-DA96-BF4C-80F9-BFE5DC59B8C1}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{C52A6B2E-3AE3-3848-B1F7-02D66D633EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7FCF268-394D-2F44-99C7-D6D2544E3375}"/>
   <bookViews>
-    <workbookView xWindow="16180" yWindow="660" windowWidth="14060" windowHeight="17480" xr2:uid="{76B42AAD-E78D-5C47-A529-CA0D1ECA81C5}"/>
+    <workbookView xWindow="16180" yWindow="660" windowWidth="14060" windowHeight="17480" activeTab="1" xr2:uid="{76B42AAD-E78D-5C47-A529-CA0D1ECA81C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Teams" sheetId="1" r:id="rId1"/>
@@ -832,6 +832,13 @@
       <c r="C2" t="s">
         <v>27</v>
       </c>
+      <c r="D2">
+        <f>30+7</f>
+        <v>37</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
@@ -843,6 +850,13 @@
       <c r="C3" t="s">
         <v>26</v>
       </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <f>30+7</f>
+        <v>37</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
@@ -854,6 +868,14 @@
       <c r="C4" t="s">
         <v>21</v>
       </c>
+      <c r="D4">
+        <f>20+6</f>
+        <v>26</v>
+      </c>
+      <c r="E4">
+        <f>10+5</f>
+        <v>15</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
@@ -865,6 +887,13 @@
       <c r="C5" t="s">
         <v>31</v>
       </c>
+      <c r="D5">
+        <f>30+8</f>
+        <v>38</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
@@ -876,6 +905,13 @@
       <c r="C6" t="s">
         <v>32</v>
       </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <f>30+9</f>
+        <v>39</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
@@ -887,6 +923,13 @@
       <c r="C7" t="s">
         <v>33</v>
       </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <f>30+7</f>
+        <v>37</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
@@ -898,6 +941,13 @@
       <c r="C8" t="s">
         <v>8</v>
       </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8">
+        <f>30+7</f>
+        <v>37</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
@@ -909,6 +959,13 @@
       <c r="C9" t="s">
         <v>10</v>
       </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <f>30+9</f>
+        <v>39</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
@@ -920,6 +977,13 @@
       <c r="C10" t="s">
         <v>11</v>
       </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <f>30+7</f>
+        <v>37</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
@@ -931,6 +995,14 @@
       <c r="C11" t="s">
         <v>16</v>
       </c>
+      <c r="D11">
+        <f>20+6</f>
+        <v>26</v>
+      </c>
+      <c r="E11">
+        <f>10+5</f>
+        <v>15</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
@@ -942,6 +1014,13 @@
       <c r="C12" t="s">
         <v>18</v>
       </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12">
+        <f>30+7</f>
+        <v>37</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
@@ -953,6 +1032,13 @@
       <c r="C13" t="s">
         <v>19</v>
       </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13">
+        <f>30+7</f>
+        <v>37</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
@@ -964,6 +1050,13 @@
       <c r="C14" t="s">
         <v>7</v>
       </c>
+      <c r="D14">
+        <f>30+8</f>
+        <v>38</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
@@ -975,6 +1068,13 @@
       <c r="C15" t="s">
         <v>4</v>
       </c>
+      <c r="D15">
+        <f>30+8</f>
+        <v>38</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
@@ -985,6 +1085,13 @@
       </c>
       <c r="C16" t="s">
         <v>6</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16">
+        <f>30+8</f>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">

--- a/src/teams.xlsx
+++ b/src/teams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a2db4df0a309fda/Labs/ConcourCast/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="8_{C52A6B2E-3AE3-3848-B1F7-02D66D633EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7FCF268-394D-2F44-99C7-D6D2544E3375}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="8_{C52A6B2E-3AE3-3848-B1F7-02D66D633EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D60927B-44A6-2A46-AEEE-353D6FF83CC1}"/>
   <bookViews>
     <workbookView xWindow="16180" yWindow="660" windowWidth="14060" windowHeight="17480" activeTab="1" xr2:uid="{76B42AAD-E78D-5C47-A529-CA0D1ECA81C5}"/>
   </bookViews>
@@ -833,8 +833,7 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <f>30+7</f>
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -854,8 +853,7 @@
         <v>4</v>
       </c>
       <c r="E3">
-        <f>30+7</f>
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -869,12 +867,10 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <f>20+6</f>
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <f>10+5</f>
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -888,8 +884,7 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <f>30+8</f>
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -909,8 +904,7 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <f>30+9</f>
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -927,8 +921,7 @@
         <v>4</v>
       </c>
       <c r="E7">
-        <f>30+7</f>
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -945,8 +938,7 @@
         <v>4</v>
       </c>
       <c r="E8">
-        <f>30+7</f>
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -963,8 +955,7 @@
         <v>2</v>
       </c>
       <c r="E9">
-        <f>30+9</f>
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -981,8 +972,7 @@
         <v>4</v>
       </c>
       <c r="E10">
-        <f>30+7</f>
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -996,12 +986,10 @@
         <v>16</v>
       </c>
       <c r="D11">
-        <f>20+6</f>
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E11">
-        <f>10+5</f>
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -1018,8 +1006,7 @@
         <v>4</v>
       </c>
       <c r="E12">
-        <f>30+7</f>
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -1036,8 +1023,7 @@
         <v>4</v>
       </c>
       <c r="E13">
-        <f>30+7</f>
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -1051,8 +1037,7 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <f>30+8</f>
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1069,8 +1054,7 @@
         <v>4</v>
       </c>
       <c r="D15">
-        <f>30+8</f>
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -1085,13 +1069,6 @@
       </c>
       <c r="C16" t="s">
         <v>6</v>
-      </c>
-      <c r="D16">
-        <v>3</v>
-      </c>
-      <c r="E16">
-        <f>30+8</f>
-        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">

--- a/src/teams.xlsx
+++ b/src/teams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a2db4df0a309fda/Labs/ConcourCast/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="8_{C52A6B2E-3AE3-3848-B1F7-02D66D633EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D60927B-44A6-2A46-AEEE-353D6FF83CC1}"/>
+  <xr:revisionPtr revIDLastSave="145" documentId="8_{C52A6B2E-3AE3-3848-B1F7-02D66D633EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF2115C2-92DB-2149-82AA-5597A4761DFE}"/>
   <bookViews>
     <workbookView xWindow="16180" yWindow="660" windowWidth="14060" windowHeight="17480" activeTab="1" xr2:uid="{76B42AAD-E78D-5C47-A529-CA0D1ECA81C5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="43">
   <si>
     <t>TeamName</t>
   </si>
@@ -163,6 +163,9 @@
   </si>
   <si>
     <t>B</t>
+  </si>
+  <si>
+    <t>Dublin</t>
   </si>
 </sst>
 </file>
@@ -799,7 +802,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7346810-13BC-6A47-9B4E-62C094287499}">
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.83203125" bestFit="1" customWidth="1"/>
@@ -1040,7 +1043,7 @@
         <v>8</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -1070,8 +1073,14 @@
       <c r="C16" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2</v>
       </c>
@@ -1081,8 +1090,14 @@
       <c r="C17" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D17">
+        <v>6</v>
+      </c>
+      <c r="E17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2</v>
       </c>
@@ -1092,8 +1107,14 @@
       <c r="C18" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D18">
+        <v>7</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>2</v>
       </c>
@@ -1103,8 +1124,14 @@
       <c r="C19" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D19">
+        <v>7</v>
+      </c>
+      <c r="E19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>2</v>
       </c>
@@ -1114,8 +1141,14 @@
       <c r="C20" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D20">
+        <v>5</v>
+      </c>
+      <c r="E20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>2</v>
       </c>
@@ -1125,8 +1158,14 @@
       <c r="C21" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>2</v>
       </c>
@@ -1136,8 +1175,14 @@
       <c r="C22" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D22">
+        <v>6</v>
+      </c>
+      <c r="E22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>2</v>
       </c>
@@ -1147,8 +1192,14 @@
       <c r="C23" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>2</v>
       </c>
@@ -1158,8 +1209,14 @@
       <c r="C24" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D24">
+        <v>6</v>
+      </c>
+      <c r="E24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>2</v>
       </c>
@@ -1169,8 +1226,14 @@
       <c r="C25" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D25">
+        <v>8</v>
+      </c>
+      <c r="E25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>2</v>
       </c>
@@ -1180,8 +1243,14 @@
       <c r="C26" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>2</v>
       </c>
@@ -1191,8 +1260,14 @@
       <c r="C27" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>2</v>
       </c>
@@ -1202,49 +1277,73 @@
       <c r="C28" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D28">
+        <v>7</v>
+      </c>
+      <c r="E28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B29" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29">
+        <v>9</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30">
+        <v>6</v>
+      </c>
+      <c r="E30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>3</v>
+      </c>
+      <c r="B32" t="s">
         <v>23</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C32" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>3</v>
-      </c>
-      <c r="B30" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>3</v>
-      </c>
-      <c r="B31" t="s">
-        <v>20</v>
-      </c>
-      <c r="C31" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>3</v>
-      </c>
-      <c r="B32" t="s">
-        <v>29</v>
-      </c>
-      <c r="C32" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -1252,10 +1351,10 @@
         <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C33" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -1263,10 +1362,10 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C34" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1274,10 +1373,10 @@
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C35" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -1285,10 +1384,10 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C36" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -1296,10 +1395,10 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C37" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -1307,10 +1406,10 @@
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -1318,10 +1417,10 @@
         <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -1329,10 +1428,10 @@
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C40" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -1340,10 +1439,10 @@
         <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C41" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -1351,10 +1450,10 @@
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="C42" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -1362,43 +1461,43 @@
         <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C45" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B46" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C46" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
@@ -1406,10 +1505,10 @@
         <v>4</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C47" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -1417,10 +1516,10 @@
         <v>4</v>
       </c>
       <c r="B48" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C48" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -1428,10 +1527,10 @@
         <v>4</v>
       </c>
       <c r="B49" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C49" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
@@ -1439,10 +1538,10 @@
         <v>4</v>
       </c>
       <c r="B50" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -1450,10 +1549,10 @@
         <v>4</v>
       </c>
       <c r="B51" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C51" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
@@ -1461,10 +1560,10 @@
         <v>4</v>
       </c>
       <c r="B52" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C52" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
@@ -1472,10 +1571,10 @@
         <v>4</v>
       </c>
       <c r="B53" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
@@ -1483,10 +1582,10 @@
         <v>4</v>
       </c>
       <c r="B54" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C54" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -1494,10 +1593,10 @@
         <v>4</v>
       </c>
       <c r="B55" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
@@ -1505,10 +1604,10 @@
         <v>4</v>
       </c>
       <c r="B56" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C56" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
@@ -1516,10 +1615,10 @@
         <v>4</v>
       </c>
       <c r="B57" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C57" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
@@ -1527,43 +1626,43 @@
         <v>4</v>
       </c>
       <c r="B58" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C58" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B59" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C59" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B60" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C60" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B61" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
@@ -1571,10 +1670,10 @@
         <v>5</v>
       </c>
       <c r="B62" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C62" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
@@ -1582,10 +1681,10 @@
         <v>5</v>
       </c>
       <c r="B63" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C63" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
@@ -1593,10 +1692,10 @@
         <v>5</v>
       </c>
       <c r="B64" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C64" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
@@ -1604,10 +1703,10 @@
         <v>5</v>
       </c>
       <c r="B65" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C65" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -1615,10 +1714,10 @@
         <v>5</v>
       </c>
       <c r="B66" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C66" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
@@ -1626,10 +1725,10 @@
         <v>5</v>
       </c>
       <c r="B67" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C67" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
@@ -1637,10 +1736,10 @@
         <v>5</v>
       </c>
       <c r="B68" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C68" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
@@ -1648,10 +1747,10 @@
         <v>5</v>
       </c>
       <c r="B69" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
@@ -1659,10 +1758,10 @@
         <v>5</v>
       </c>
       <c r="B70" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C70" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
@@ -1670,10 +1769,10 @@
         <v>5</v>
       </c>
       <c r="B71" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C71" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
@@ -1681,10 +1780,10 @@
         <v>5</v>
       </c>
       <c r="B72" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C72" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
@@ -1692,9 +1791,42 @@
         <v>5</v>
       </c>
       <c r="B73" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>5</v>
+      </c>
+      <c r="B74" t="s">
+        <v>2</v>
+      </c>
+      <c r="C74" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>5</v>
+      </c>
+      <c r="B75" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>5</v>
+      </c>
+      <c r="B76" t="s">
         <v>6</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C76" t="s">
         <v>4</v>
       </c>
     </row>

--- a/src/teams.xlsx
+++ b/src/teams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a2db4df0a309fda/Labs/ConcourCast/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="145" documentId="8_{C52A6B2E-3AE3-3848-B1F7-02D66D633EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF2115C2-92DB-2149-82AA-5597A4761DFE}"/>
+  <xr:revisionPtr revIDLastSave="175" documentId="8_{C52A6B2E-3AE3-3848-B1F7-02D66D633EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D18D0AC9-93F6-9B4A-A17D-401BD766CA59}"/>
   <bookViews>
     <workbookView xWindow="16180" yWindow="660" windowWidth="14060" windowHeight="17480" activeTab="1" xr2:uid="{76B42AAD-E78D-5C47-A529-CA0D1ECA81C5}"/>
   </bookViews>
@@ -1345,8 +1345,14 @@
       <c r="C32" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D32">
+        <v>7</v>
+      </c>
+      <c r="E32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>3</v>
       </c>
@@ -1356,8 +1362,14 @@
       <c r="C33" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D33">
+        <v>3</v>
+      </c>
+      <c r="E33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>3</v>
       </c>
@@ -1367,8 +1379,14 @@
       <c r="C34" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D34">
+        <v>9</v>
+      </c>
+      <c r="E34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>3</v>
       </c>
@@ -1378,8 +1396,14 @@
       <c r="C35" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D35">
+        <v>7</v>
+      </c>
+      <c r="E35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>3</v>
       </c>
@@ -1389,8 +1413,14 @@
       <c r="C36" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D36">
+        <v>7</v>
+      </c>
+      <c r="E36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>3</v>
       </c>
@@ -1400,8 +1430,14 @@
       <c r="C37" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D37">
+        <v>6</v>
+      </c>
+      <c r="E37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>3</v>
       </c>
@@ -1411,8 +1447,14 @@
       <c r="C38" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D38">
+        <v>9</v>
+      </c>
+      <c r="E38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>3</v>
       </c>
@@ -1422,8 +1464,14 @@
       <c r="C39" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D39">
+        <v>4</v>
+      </c>
+      <c r="E39">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>3</v>
       </c>
@@ -1433,8 +1481,14 @@
       <c r="C40" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>3</v>
       </c>
@@ -1444,8 +1498,14 @@
       <c r="C41" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D41">
+        <v>7</v>
+      </c>
+      <c r="E41">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>3</v>
       </c>
@@ -1455,8 +1515,14 @@
       <c r="C42" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D42">
+        <v>3</v>
+      </c>
+      <c r="E42">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>3</v>
       </c>
@@ -1466,8 +1532,14 @@
       <c r="C43" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D43">
+        <v>9</v>
+      </c>
+      <c r="E43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>3</v>
       </c>
@@ -1477,8 +1549,14 @@
       <c r="C44" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D44">
+        <v>4</v>
+      </c>
+      <c r="E44">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>3</v>
       </c>
@@ -1488,8 +1566,14 @@
       <c r="C45" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D45">
+        <v>5</v>
+      </c>
+      <c r="E45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>3</v>
       </c>
@@ -1499,8 +1583,14 @@
       <c r="C46" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D46">
+        <v>9</v>
+      </c>
+      <c r="E46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>4</v>
       </c>
@@ -1511,7 +1601,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>4</v>
       </c>

--- a/src/teams.xlsx
+++ b/src/teams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a2db4df0a309fda/Labs/ConcourCast/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="175" documentId="8_{C52A6B2E-3AE3-3848-B1F7-02D66D633EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D18D0AC9-93F6-9B4A-A17D-401BD766CA59}"/>
+  <xr:revisionPtr revIDLastSave="178" documentId="8_{C52A6B2E-3AE3-3848-B1F7-02D66D633EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E013B543-3FB4-1C4A-B9F1-FB0F6A99E169}"/>
   <bookViews>
     <workbookView xWindow="16180" yWindow="660" windowWidth="14060" windowHeight="17480" activeTab="1" xr2:uid="{76B42AAD-E78D-5C47-A529-CA0D1ECA81C5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="42">
   <si>
     <t>TeamName</t>
   </si>
@@ -163,9 +163,6 @@
   </si>
   <si>
     <t>B</t>
-  </si>
-  <si>
-    <t>Dublin</t>
   </si>
 </sst>
 </file>
@@ -1326,7 +1323,7 @@
         <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="D31">
         <v>4</v>
@@ -1374,7 +1371,7 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
         <v>26</v>
@@ -1620,7 +1617,7 @@
         <v>24</v>
       </c>
       <c r="C49" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">

--- a/src/teams.xlsx
+++ b/src/teams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a2db4df0a309fda/Labs/ConcourCast/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="178" documentId="8_{C52A6B2E-3AE3-3848-B1F7-02D66D633EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E013B543-3FB4-1C4A-B9F1-FB0F6A99E169}"/>
+  <xr:revisionPtr revIDLastSave="208" documentId="8_{C52A6B2E-3AE3-3848-B1F7-02D66D633EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D534E49B-836C-104E-9F01-9EA5042F0D6C}"/>
   <bookViews>
     <workbookView xWindow="16180" yWindow="660" windowWidth="14060" windowHeight="17480" activeTab="1" xr2:uid="{76B42AAD-E78D-5C47-A529-CA0D1ECA81C5}"/>
   </bookViews>
@@ -1597,6 +1597,12 @@
       <c r="C47" t="s">
         <v>23</v>
       </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47">
+        <v>8</v>
+      </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48">
@@ -1608,8 +1614,14 @@
       <c r="C48" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D48">
+        <v>5</v>
+      </c>
+      <c r="E48">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>4</v>
       </c>
@@ -1619,8 +1631,14 @@
       <c r="C49" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D49">
+        <v>2</v>
+      </c>
+      <c r="E49">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>4</v>
       </c>
@@ -1630,8 +1648,14 @@
       <c r="C50" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D50">
+        <v>3</v>
+      </c>
+      <c r="E50">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>4</v>
       </c>
@@ -1641,8 +1665,14 @@
       <c r="C51" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D51">
+        <v>5</v>
+      </c>
+      <c r="E51">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>4</v>
       </c>
@@ -1652,8 +1682,14 @@
       <c r="C52" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D52">
+        <v>8</v>
+      </c>
+      <c r="E52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>4</v>
       </c>
@@ -1663,8 +1699,14 @@
       <c r="C53" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D53">
+        <v>6</v>
+      </c>
+      <c r="E53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>4</v>
       </c>
@@ -1674,8 +1716,14 @@
       <c r="C54" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D54">
+        <v>5</v>
+      </c>
+      <c r="E54">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>4</v>
       </c>
@@ -1685,8 +1733,14 @@
       <c r="C55" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D55">
+        <v>7</v>
+      </c>
+      <c r="E55">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>4</v>
       </c>
@@ -1696,8 +1750,14 @@
       <c r="C56" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D56">
+        <v>2</v>
+      </c>
+      <c r="E56">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>4</v>
       </c>
@@ -1707,8 +1767,14 @@
       <c r="C57" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D57">
+        <v>8</v>
+      </c>
+      <c r="E57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>4</v>
       </c>
@@ -1718,8 +1784,14 @@
       <c r="C58" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D58">
+        <v>8</v>
+      </c>
+      <c r="E58">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>4</v>
       </c>
@@ -1729,8 +1801,14 @@
       <c r="C59" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D59">
+        <v>4</v>
+      </c>
+      <c r="E59">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>4</v>
       </c>
@@ -1740,8 +1818,14 @@
       <c r="C60" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D60">
+        <v>3</v>
+      </c>
+      <c r="E60">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>4</v>
       </c>
@@ -1751,8 +1835,14 @@
       <c r="C61" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D61">
+        <v>9</v>
+      </c>
+      <c r="E61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>5</v>
       </c>
@@ -1763,7 +1853,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>5</v>
       </c>
@@ -1774,7 +1864,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>5</v>
       </c>
